--- a/Result/checksun_type/電纜.xlsx
+++ b/Result/checksun_type/電纜.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>138.0</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>144.7</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>158.31</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>144.7</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>158.31</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>126140252.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>179646773.6</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>179646773.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>288541776.1</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>249860076.6</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>249860076.6</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-13008524.13905758</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>126140252</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>126140252.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>135.6</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>145.35</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>158.83</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>145.35</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>158.83</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>149355643.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>199168061.0</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>199168061</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>286806442.7</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>252995092.08</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>252995092.08</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-5288395.852468729</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>149355643</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>149355643.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>133.9</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>146.28</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>159.48</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>146.28</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>159.48</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>236429825.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>243968869.0</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>243968869</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>280669574.0</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>255272113.08</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>255272113.08</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>3441866.801674962</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>236429825</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>236429825.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>132.9</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>147.28</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>160.17</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>147.28</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>160.17</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>173429988.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>305348589.0</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>305348589</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>272591978.0</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>254388028.92</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>254388028.92</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>6461370.136106104</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>173429988</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>173429988.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>133.4</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>148.32</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>160.95</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>148.32</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>160.95</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>212878160.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>421450515.0</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>421450515</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>274650710.4</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>254522728.7</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>254522728.7</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>17294165.64471823</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>212878160</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>212878160.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>136.3</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>149.6</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>161.73</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>149.6</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>161.73</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>223746689.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>397436778.6</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>397436778.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>263301806.5</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>254911229.58</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>254911229.58</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>27925349.16970986</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>223746689</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>223746689.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>140.1</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>151.12</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>162.59</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>151.12</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>162.59</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>373359683.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>374444824.4</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>374444824.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>252575891.8</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>255257682.72</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>255257682.72</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>40950935.056494</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>373359683</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>373359683.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>143.9</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>152.65</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>163.44</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>152.65</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>163.44</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>543328425.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>317370279.0</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>317370279</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>231842549.9</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>254515985.98</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>254515985.98</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>42066417.85702515</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>543328425</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>543328425.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>147.2</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>154.25</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>164.29</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>154.25</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>164.29</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>753939618.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>239835367.0</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>239835367</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>202283159.5</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>250790390.86</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>250790390.86</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>23946656.00574735</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>753939618</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>753939618.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>149.6</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>155.78</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>165.1</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>155.78</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>165.1</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>92809478.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>127850905.8</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>127850905.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>148995940.1</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>248204610.78</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>248204610.78</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-25359440.74628332</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>92809478</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>92809478.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>150.2</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>156.57</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>165.78</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>156.57</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>165.78</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>108786918.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>129166834.4</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>129166834.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>167987433.4</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>261232164.76</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>261232164.76</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-24055655.36538848</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>108786918</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>108786918.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>41.02</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>42.8</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>44.44</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>44.44</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>15763104.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>16642260.4</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>16642260.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>24925115.9</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>52770777.32</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>52770777.32</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-6278896.056399416</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>15763104</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>15763104.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>40.76000000000001</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>42.91</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>44.55</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>42.91</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>44.55</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>10342159.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>19565966.2</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>19565966.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>27503143.8</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>55497104.44</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>55497104.44</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-6383160.863354962</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>10342159</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>10342159.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>40.76000000000001</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>43.08</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>44.72</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>43.08</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>44.72</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>14621248.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>24291502.8</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>24291502.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>30729261.6</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>60114965.94</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>60114965.94</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-5723325.021028779</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>14621248</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>14621248.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>41.07000000000001</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>43.28</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>44.88</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>43.28</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>44.88</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>26314342.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>27390720.6</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>27390720.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>31823661.0</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>67650631.36</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>67650631.36</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-5034771.745526068</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>26314342</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>26314342.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>41.59</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>43.47</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>45.02</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>43.47</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>45.02</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>16170449.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>28391282.0</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>28391282</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>35985353.1</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>68297992.24</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>68297992.23999999</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-5124142.432467684</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>16170449</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>16170449.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>42.17</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>43.64</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>45.13</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>43.64</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>45.13</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>30381633.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>33207971.4</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>33207971.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>42432138.5</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>69549254.3</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>69549254.3</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-3981964.076939009</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>30381633</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>30381633.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>42.75</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>43.85</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>45.26</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>43.85</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>45.26</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>33969842.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>35440321.4</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>35440321.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>42408341.5</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>70679971.12</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>70679971.12</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-3730694.566293083</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>33969842</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>33969842.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>43.29</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>44.03</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>45.36</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>44.03</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>45.36</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>30117337.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>37167020.4</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>37167020.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>48483797.1</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>70769330.02</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>70769330.02</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-3622949.995145567</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>30117337</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>30117337.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>43.34</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>44.14</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>45.43</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>44.14</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>45.43</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>31317149.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>36256601.4</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>36256601.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>54122064.5</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>71668700.06</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>71668700.06</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-2926869.715108208</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>31317149</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>31317149.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>43.23</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>44.22</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>45.5</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>44.22</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>45.5</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>40253896.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>43579424.2</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>43579424.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>56861420.0</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>73056375.76</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>73056375.76000001</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-1956489.539515264</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>40253896</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>40253896.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>43.16</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>44.22</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>45.57</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>44.22</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>45.57</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>41543383.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>51656305.6</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>51656305.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>57668449.0</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>74198759.34</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>74198759.34</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-1457866.12654265</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>41543383</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>41543383.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>47.7</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>47.25</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>47.5</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>47.25</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>47.5</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>2694578.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>3879862.6</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>3879862.6</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>6314058.8</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>6317096.46</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>6317096.46</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-666790.0029675178</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>2694578</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>2694578.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>47.64</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>47.16</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>47.55</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>47.16</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>47.55</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>1592436.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>4334872.2</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>4334872.2</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>7828925.6</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>6473797.62</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>6473797.62</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-536660.9152201777</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>1592436</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>1592436.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>47.62</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>47.06</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>47.59</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>47.06</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>47.59</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>4438311.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>5100960.4</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>5100960.4</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>8080192.8</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>6613318.26</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>6613318.26</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-213509.1143232584</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>4438311</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>4438311.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>47.77</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>47.0</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>47.63</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>47</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>47.63</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>4983111.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>5511257.8</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>5511257.8</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>8706769.3</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>6906120.1</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>6906120.1</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-49153.53753039986</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>4983111</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>4983111.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>48.0</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>46.89</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>47.67</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>46.89</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>47.67</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>5690877.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>6639050.8</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>6639050.8</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>8381166.2</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>7037984.02</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>7037984.02</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>129024.1985140545</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>5690877</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>5690877.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>48.13</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>46.76</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>47.71</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>46.76</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>47.71</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>4969626.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>8748255.0</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>8748255</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>7946447.0</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>7001537.76</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>7001537.76</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>303123.7429163456</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>4969626</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>4969626.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>48.41999999999999</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>46.68</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>47.78</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>46.68</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>47.78</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>5422877.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>11322979.0</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>11322979</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>7715670.4</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>7000520.92</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>7000520.92</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>618288.422672607</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>5422877</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>5422877.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>48.37</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>46.59</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>47.82</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>46.59</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>47.82</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>6489798.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>11059425.2</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>11059425.2</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>7630443.0</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>6989184.84</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>6989184.84</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>997879.3429432437</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>6489798</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>6489798.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>48.17</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>46.47</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>47.86</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>46.47</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>47.86</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>10622076.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>11902280.8</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>11902280.8</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>7416551.7</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>6957466.84</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>6957466.84</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>1390200.573939038</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>10622076</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>10622076.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>47.57</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>46.33</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>47.88</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>46.33</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>47.88</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>16236898.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>10123281.6</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>10123281.6</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>7041660.8</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>6869074.96</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>6869074.96</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>1458265.383435206</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>16236898</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>16236898.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>47.04</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>46.2</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>47.9</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>47.9</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>17843246.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>7144639.0</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>7144639</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>5782174.6</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>6611680.04</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>6611680.04</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>901831.8475927627</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>17843246</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>17843246.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>34.88</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>36.7</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>37.32</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>37.32</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>25692254.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>29440601.4</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>29440601.4</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>42524330.5</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>82754235.42</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>82754235.42</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-13937831.31322654</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>25692254</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>25692254.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>34.64</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>36.87</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>37.34</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>36.87</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>37.34</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>18000285.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>31244812.8</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>31244812.8</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>45569514.5</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>83106878.6</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>83106878.59999999</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-14129874.73679522</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>18000285</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>18000285.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>34.51000000000001</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>37.09</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>37.37</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>37.09</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>37.37</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>31057221.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>39804412.8</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>39804412.8</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>51161298.4</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>83601620.82</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>83601620.81999999</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-13075444.56557922</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>31057221</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>31057221.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>34.59999999999999</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>37.32</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>37.4</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>37.32</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>37.4</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>47433378.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>47059217.0</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>47059217</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>70585441.3</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>84707045.68</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>84707045.68000001</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-12501093.0150714</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>47433378</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>47433378.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>34.83</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>37.51</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>37.42</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>37.51</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>37.42</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>25019869.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>47574410.0</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>47574410</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>73192502.5</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>84948018.32</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>84948018.31999999</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-12988711.4423791</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>25019869</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>25019869.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>35.13</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>37.7</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>37.45</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>37.45</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>34713311.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>55608059.6</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>55608059.6</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>82385341.1</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>86401244.22</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>86401244.22</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-10819979.25130512</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>34713311</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>34713311.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>35.51</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>37.95</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>37.52</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>37.95</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>37.52</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>60798285.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>59894216.2</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>59894216.2</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>89794563.3</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>86991482.84</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>86991482.84</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>-8373945.647938564</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>60798285</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>60798285.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>35.86</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>38.15</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>37.56</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>38.15</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>37.56</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>67331242.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>62518184.0</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>62518184</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>98664993.6</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>86408970.8</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>86408970.8</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>-7375361.084274217</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>67331242</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>67331242.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>35.95</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>38.31</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>37.58</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>38.31</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>37.58</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>50009343.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>94111665.6</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>94111665.59999999</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>112721053.6</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>86187783.64</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>86187783.64</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-6385365.633172527</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>50009343</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>50009343.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>36.5</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>38.46</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>37.59</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>38.46</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>37.59</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>65188117.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>98810595.0</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>98810595</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>131948481.5</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>86974983.42</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>86974983.42</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-2887119.894699648</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>65188117</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>65188117.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>37.07000000000001</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>38.56</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>37.62</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>38.56</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>37.62</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>56144094.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>109162622.6</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>109162622.6</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>136721621.2</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>86663205.08</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>86663205.08</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>587188.2279294282</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>56144094</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>56144094.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>38.36</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>39.89</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>40.46</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>39.89</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>40.46</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>177927513.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>140697538.0</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>140697538</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>260992136.9</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>330018402.76</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>330018402.76</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-48088936.63194677</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>177927513</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>177927513.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>38.09</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>39.97</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>40.48</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>39.97</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>40.48</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>99428848.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>152639232.6</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>152639232.6</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>260750157.7</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>333330629.36</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>333330629.36</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-52011927.30912569</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>99428848</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>99428848.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>38.01000000000001</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>40.1</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>40.55</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>40.55</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>89920913.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>174410900.4</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>174410900.4</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>267478554.6</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>337517119.18</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>337517119.18</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-47348059.62262681</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>89920913</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>89920913.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>38.27</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>40.3</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>40.63</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>40.63</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>181437844.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>208575579.2</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>208575579.2</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>297737400.3</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>342812696.14</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>342812696.14</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-37975682.04824883</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>181437844</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>181437844.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>38.8</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>40.46</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>40.7</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>40.46</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>40.7</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>154772572.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>245779825.4</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>245779825.4</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>343489080.4</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>348480442.44</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>348480442.44</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-33035682.33312863</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>154772572</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>154772572.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>39.39</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>40.59</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>40.76</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>40.59</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>40.76</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>237635986.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>381286735.8</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>381286735.8</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>385340961.8</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>363305015.06</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>363305015.06</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>-21941700.65677369</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>237635986</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>237635986.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>39.7</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>40.8</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>40.88</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>40.88</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>208287187.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>368861082.8</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>368861082.8</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>396930157.4</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>378282020.1</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>378282020.1</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>-14187746.16709614</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>208287187</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>208287187.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>39.8</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>41.02</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>40.93</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>41.02</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>40.93</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>260744307.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>360546208.8</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>360546208.8</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>446159580.7</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>377236784.22</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>377236784.22</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>540551.0741251707</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>260744307</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>260744307.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>39.63</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>41.19</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>40.96</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>41.19</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>40.96</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>367459075.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>386899221.4</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>386899221.4</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>472908582.9</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>376778985.7</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>376778985.7</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>15941264.59465122</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>367459075</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>367459075.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>39.56</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>41.3</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>40.98</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>40.98</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>832307124.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>441198335.4</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>441198335.4</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>512525775.0</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>376348073.72</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>376348073.72</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>25939227.88845086</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>832307124</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>832307124.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>39.6</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>41.28</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>40.99</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>41.28</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>40.99</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>175507721.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>389395187.8</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>389395187.8</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>458359359.9</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>369237286.4</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>369237286.4</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>-10509516.50928009</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>175507721</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>175507721.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>28.99</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>30.08</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>28.2</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>30.08</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>28.2</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>1203482068.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>1387618376.8</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>1387618376.8</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>4264040487.3</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>3111629550.18</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>3111629550.18</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-488176249.5318046</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>1203482068</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>1203482068.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>29.02</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>30.16</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>28.07</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>30.16</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>28.07</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>942023312.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>1584381817.0</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>1584381817</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>4484329546.0</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>3097694126.7</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>3097694126.7</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-425650424.2230182</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>942023312</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>942023312.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>29.25</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>30.24</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>27.94</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>30.24</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>27.94</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>1007778782.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>2139497377.6</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>2139497377.6</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>4665494634.0</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>3096337448.26</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>3096337448.26</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-293112577.631073</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>1007778782</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>1007778782.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>29.73</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>30.32</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>27.81</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>30.32</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>27.81</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>1607084998.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>3258049059.4</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>3258049059.4</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>4688553902.3</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>3083594155.06</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>3083594155.06</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>-100349719.3700418</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>1607084998</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>1607084998.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>30.62</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>30.38</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>27.69</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>30.38</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>27.69</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>2177722724.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>5262265961.4</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>5262265961.4</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>4687463430.7</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>3075231109.06</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>3075231109.06</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>114398330.6946478</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>2177722724</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>2177722724.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>31.58</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>30.41</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>27.56</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>30.41</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>27.56</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>2187299269.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>7140462597.8</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>7140462597.8</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>4678699401.4</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>3064464439.28</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>3064464439.28</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>355955848.3336811</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>2187299269</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>2187299269.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>32.04</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>30.44</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>27.46</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>30.44</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>27.46</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>3717601115.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>7384277275.0</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>7384277275</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>4600886187.9</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>3041422265.56</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>3041422265.56</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>687299249.1275253</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>3717601115</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>3717601115.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>32.03</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>30.45</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>27.29</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>30.45</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>27.29</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>6600537191.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>7191491890.4</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>7191491890.4</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>4454153458.5</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>2973288757.28</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>2973288757.28</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>972139650.7213211</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>6600537191</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>6600537191.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>31.7</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>30.34</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>27.1</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>30.34</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>27.1</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>11628169508.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>6119058745.2</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>6119058745.2</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>3965899981.1</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>2847760321.4</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>2847760321.4</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>1035449228.758123</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>11628169508</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>11628169508.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>31.07</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>30.19</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>26.9</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>30.19</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>26.9</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>11568705906.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>4112660900.0</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>4112660900</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>2972243250.2</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>2623033685.92</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>2623033685.92</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>550236262.3907671</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>11568705906</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>11568705906.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>30.27</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>29.82</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>26.66</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>29.82</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>26.66</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>3406372655.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>2216936205.0</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>2216936205</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>2119863690.1</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>2406749639.6</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>2406749639.6</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>-156205313.0051274</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>3406372655</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>3406372655.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
